--- a/Relaciones totales libro-patrimonio/LIBRO PATRIMONIO MATERIAL.xlsx
+++ b/Relaciones totales libro-patrimonio/LIBRO PATRIMONIO MATERIAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0A8532-BBD2-496E-A6D2-99EA7A007E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83901C01-7C79-4285-913D-A24A480B9017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monumentos" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,26 @@
     <sheet name="camino y viaje" sheetId="4" r:id="rId4"/>
     <sheet name="Espacios naturales" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="272">
   <si>
     <t>RELATOS DE VIAJES ANGLOSAJONES (1900-1914)</t>
   </si>
@@ -352,15 +361,6 @@
     <t>Tajo</t>
   </si>
   <si>
-    <t>total espacios naturales</t>
-  </si>
-  <si>
-    <t>total de caminos y viajes</t>
-  </si>
-  <si>
-    <t>total de comida y bebida</t>
-  </si>
-  <si>
     <t>total de espacios públicos</t>
   </si>
   <si>
@@ -791,6 +791,204 @@
   </si>
   <si>
     <t>23 (15+4+2+1+1)</t>
+  </si>
+  <si>
+    <t>67 (56+7+4)</t>
+  </si>
+  <si>
+    <t>65 (53+12)</t>
+  </si>
+  <si>
+    <t>46 (45+1)</t>
+  </si>
+  <si>
+    <t>86 (45+36+5)</t>
+  </si>
+  <si>
+    <t>35 (29+6)</t>
+  </si>
+  <si>
+    <t>59 (29+29+1)</t>
+  </si>
+  <si>
+    <t>29 (21+8)</t>
+  </si>
+  <si>
+    <t>32 (17+15)</t>
+  </si>
+  <si>
+    <t>29 (14+12+3)</t>
+  </si>
+  <si>
+    <t>52 (26+13+12+1)</t>
+  </si>
+  <si>
+    <t>8 (7+1)</t>
+  </si>
+  <si>
+    <t>9 (7+2)</t>
+  </si>
+  <si>
+    <t>10 (5+5)</t>
+  </si>
+  <si>
+    <t>9 (4+3+2)</t>
+  </si>
+  <si>
+    <t>20 (16+2+2)</t>
+  </si>
+  <si>
+    <t>19 (18+1)</t>
+  </si>
+  <si>
+    <t>5 (2+1+1+1)</t>
+  </si>
+  <si>
+    <t>7 (5+1+1)</t>
+  </si>
+  <si>
+    <t>70 (53+15+2)</t>
+  </si>
+  <si>
+    <t>42 (18+18+4+1+1)</t>
+  </si>
+  <si>
+    <t>17 (9+8)</t>
+  </si>
+  <si>
+    <t>26 (18+8)</t>
+  </si>
+  <si>
+    <t>28 (24+3+1)</t>
+  </si>
+  <si>
+    <t>39 (37+2)</t>
+  </si>
+  <si>
+    <t>12 (10+2)</t>
+  </si>
+  <si>
+    <t>26 (14+12)</t>
+  </si>
+  <si>
+    <t>33 (16+14+3)</t>
+  </si>
+  <si>
+    <t>20 (15+5)</t>
+  </si>
+  <si>
+    <t>26 (22+2+2)</t>
+  </si>
+  <si>
+    <t>11 (7+2+2)</t>
+  </si>
+  <si>
+    <t>3 (1+1+1)</t>
+  </si>
+  <si>
+    <t>8 (5+2+1)</t>
+  </si>
+  <si>
+    <t>16 (13+1+1+1)</t>
+  </si>
+  <si>
+    <t>20 (19+1)</t>
+  </si>
+  <si>
+    <t>24 (13+11)</t>
+  </si>
+  <si>
+    <t>25 (15+10)</t>
+  </si>
+  <si>
+    <t>18 (10+8)</t>
+  </si>
+  <si>
+    <t>17 (11+6)</t>
+  </si>
+  <si>
+    <t>14 (11+3)</t>
+  </si>
+  <si>
+    <t>28 (12+10+2+2+2)</t>
+  </si>
+  <si>
+    <t>28 (17+7+2+2)</t>
+  </si>
+  <si>
+    <t>25 (22+2+1)</t>
+  </si>
+  <si>
+    <t>13 (11+1+1)</t>
+  </si>
+  <si>
+    <t>39 (31+8)</t>
+  </si>
+  <si>
+    <t>6ç11 (6+5)</t>
+  </si>
+  <si>
+    <t>11 (6+5)</t>
+  </si>
+  <si>
+    <t>18 (9+5+4)</t>
+  </si>
+  <si>
+    <t>6 (3+3)</t>
+  </si>
+  <si>
+    <t>18 (15+3)</t>
+  </si>
+  <si>
+    <t>32 (18+8+3+3)</t>
+  </si>
+  <si>
+    <t>13 (11+2)</t>
+  </si>
+  <si>
+    <t>15 (9+4+2)</t>
+  </si>
+  <si>
+    <t>56 (41+15)</t>
+  </si>
+  <si>
+    <t>45 (34+11)</t>
+  </si>
+  <si>
+    <t>18 (13+5)</t>
+  </si>
+  <si>
+    <t>14 (10+4)</t>
+  </si>
+  <si>
+    <t>11 (7+4)</t>
+  </si>
+  <si>
+    <t>8 (6+1+1)</t>
+  </si>
+  <si>
+    <t>7 (4+2+1)</t>
+  </si>
+  <si>
+    <t>16 (9+7)</t>
+  </si>
+  <si>
+    <t>23 (16+7)</t>
+  </si>
+  <si>
+    <t>24 (18+6)</t>
+  </si>
+  <si>
+    <t>15 (9+6)</t>
+  </si>
+  <si>
+    <t>43 (41+2)</t>
+  </si>
+  <si>
+    <t>17 (10+3+2+2)</t>
+  </si>
+  <si>
+    <t>32 (31+1)</t>
   </si>
 </sst>
 </file>
@@ -907,7 +1105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1076,12 +1274,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1098,9 +1361,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1154,9 +1414,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1193,40 +1450,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1268,19 +1495,52 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1574,7 +1834,7 @@
     <col min="5" max="5" width="21.5546875" customWidth="1"/>
     <col min="6" max="6" width="19.6640625" customWidth="1"/>
     <col min="7" max="7" width="21.44140625" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" customWidth="1"/>
     <col min="10" max="10" width="14.109375" customWidth="1"/>
     <col min="11" max="11" width="21.5546875" customWidth="1"/>
@@ -1599,12 +1859,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1632,169 +1892,169 @@
       <c r="AC1" s="2"/>
     </row>
     <row r="2" spans="1:29" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="J2" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="L2" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="38" t="s">
+      <c r="N2" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="38" t="s">
+      <c r="O2" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="38" t="s">
+      <c r="P2" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="38" t="s">
+      <c r="Q2" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="S2" s="38" t="s">
+      <c r="R2" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="S2" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="38" t="s">
+      <c r="T2" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="U2" s="38" t="s">
+      <c r="U2" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="V2" s="38" t="s">
+      <c r="V2" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="W2" s="38" t="s">
+      <c r="W2" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="X2" s="38" t="s">
+      <c r="X2" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="Y2" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="38" t="s">
+      <c r="Z2" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="AA2" s="38" t="s">
+      <c r="AA2" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="38" t="s">
+      <c r="AB2" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="AC2" s="38" t="s">
+      <c r="AC2" s="36" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <v>1900</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="48">
         <v>31</v>
       </c>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27">
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25">
         <v>7</v>
       </c>
-      <c r="J3" s="27">
-        <v>1</v>
-      </c>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27">
+      <c r="J3" s="25">
+        <v>1</v>
+      </c>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25">
         <v>2</v>
       </c>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27">
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25">
         <v>3</v>
       </c>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25">
         <v>3</v>
       </c>
-      <c r="R3" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="S3" s="27">
+      <c r="R3" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="S3" s="25">
         <v>8</v>
       </c>
-      <c r="T3" s="60">
+      <c r="T3" s="48">
         <v>27</v>
       </c>
-      <c r="U3" s="27"/>
-      <c r="V3" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="W3" s="27">
+      <c r="U3" s="25"/>
+      <c r="V3" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="W3" s="25">
         <v>8</v>
       </c>
-      <c r="X3" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y3" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z3" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA3" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB3" s="27">
+      <c r="X3" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z3" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA3" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB3" s="25">
         <v>2</v>
       </c>
-      <c r="AC3" s="28">
+      <c r="AC3" s="26">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1806,52 +2066,52 @@
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29">
-        <v>1</v>
-      </c>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29">
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27">
+        <v>1</v>
+      </c>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27">
         <v>2</v>
       </c>
-      <c r="R4" s="62" t="s">
+      <c r="R4" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="W4" s="27">
+        <v>1</v>
+      </c>
+      <c r="X4" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="W4" s="29">
-        <v>1</v>
-      </c>
-      <c r="X4" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29">
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27">
         <v>2</v>
       </c>
-      <c r="AA4" s="29">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="29">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="30"/>
+      <c r="AA4" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="28"/>
     </row>
     <row r="5" spans="1:29" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1863,66 +2123,66 @@
       <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="50">
         <v>27</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29">
+      <c r="F5" s="27"/>
+      <c r="G5" s="27">
         <v>2</v>
       </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29">
+      <c r="H5" s="27"/>
+      <c r="I5" s="27">
         <v>2</v>
       </c>
-      <c r="J5" s="29">
-        <v>1</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29">
+      <c r="J5" s="27">
+        <v>1</v>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27">
         <v>5</v>
       </c>
-      <c r="R5" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="S5" s="29"/>
-      <c r="T5" s="62" t="s">
-        <v>175</v>
-      </c>
-      <c r="U5" s="29">
-        <v>1</v>
-      </c>
-      <c r="V5" s="29">
+      <c r="R5" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="S5" s="27"/>
+      <c r="T5" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="U5" s="27">
+        <v>1</v>
+      </c>
+      <c r="V5" s="27">
         <v>4</v>
       </c>
-      <c r="W5" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="X5" s="62" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y5" s="62" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z5" s="29">
+      <c r="W5" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="X5" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y5" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z5" s="27">
         <v>4</v>
       </c>
-      <c r="AA5" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="AB5" s="29">
+      <c r="AA5" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB5" s="27">
         <v>6</v>
       </c>
-      <c r="AC5" s="30">
+      <c r="AC5" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1934,157 +2194,203 @@
       <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="62">
+      <c r="E6" s="50">
         <v>21</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="62" t="s">
-        <v>176</v>
-      </c>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29">
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27">
         <v>5</v>
       </c>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29">
+      <c r="W6" s="27"/>
+      <c r="X6" s="27">
         <v>3</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="27">
         <v>3</v>
       </c>
-      <c r="Z6" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA6" s="29">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC6" s="30">
+      <c r="Z6" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA6" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC6" s="28">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <v>1905</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="67">
+      <c r="E7" s="53">
         <v>15</v>
       </c>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31">
+      <c r="F7" s="29"/>
+      <c r="G7" s="29">
         <v>2</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31">
+      <c r="H7" s="29"/>
+      <c r="I7" s="29">
         <v>8</v>
       </c>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31">
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29">
         <v>3</v>
       </c>
-      <c r="M7" s="31">
-        <v>1</v>
-      </c>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31">
+      <c r="M7" s="29">
+        <v>1</v>
+      </c>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29">
         <v>5</v>
       </c>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31">
+      <c r="R7" s="29"/>
+      <c r="S7" s="29">
         <v>5</v>
       </c>
-      <c r="T7" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="U7" s="31"/>
-      <c r="V7" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="W7" s="67">
+      <c r="T7" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="U7" s="29"/>
+      <c r="V7" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="W7" s="53">
         <v>12</v>
       </c>
-      <c r="X7" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y7" s="67" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z7" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA7" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB7" s="31">
+      <c r="X7" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y7" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z7" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA7" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB7" s="29">
         <v>5</v>
       </c>
-      <c r="AC7" s="32"/>
+      <c r="AC7" s="30"/>
     </row>
     <row r="8" spans="1:29" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>1908</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="33"/>
+      <c r="E8" s="55">
+        <v>40</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="G8" s="55">
+        <v>10</v>
+      </c>
+      <c r="H8" s="31">
+        <v>1</v>
+      </c>
+      <c r="I8" s="55">
+        <v>15</v>
+      </c>
+      <c r="J8" s="31">
+        <v>6</v>
+      </c>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31">
+        <v>6</v>
+      </c>
+      <c r="M8" s="31">
+        <v>1</v>
+      </c>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31">
+        <v>6</v>
+      </c>
+      <c r="P8" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="55">
+        <v>26</v>
+      </c>
+      <c r="R8" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="S8" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="T8" s="55">
+        <v>37</v>
+      </c>
+      <c r="U8" s="31">
+        <v>2</v>
+      </c>
+      <c r="V8" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="W8" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="X8" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y8" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z8" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA8" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB8" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="AC8" s="31" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="9" spans="1:29" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
@@ -2099,31 +2405,63 @@
       <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
+      <c r="E9" s="27">
+        <v>6</v>
+      </c>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27">
+        <v>1</v>
+      </c>
+      <c r="H9" s="27"/>
+      <c r="I9" s="50">
+        <v>13</v>
+      </c>
+      <c r="J9" s="50">
+        <v>10</v>
+      </c>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27">
+        <v>3</v>
+      </c>
+      <c r="R9" s="27"/>
+      <c r="S9" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="T9" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="U9" s="27">
+        <v>1</v>
+      </c>
+      <c r="V9" s="50" t="s">
+        <v>228</v>
+      </c>
+      <c r="W9" s="50">
+        <v>16</v>
+      </c>
+      <c r="X9" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y9" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z9" s="50">
+        <v>20</v>
+      </c>
+      <c r="AA9" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB9" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC9" s="27">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:29" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -2138,31 +2476,69 @@
       <c r="D10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="29"/>
+      <c r="E10" s="50">
+        <v>19</v>
+      </c>
+      <c r="F10" s="27">
+        <v>1</v>
+      </c>
+      <c r="G10" s="27">
+        <v>1</v>
+      </c>
+      <c r="H10" s="27">
+        <v>3</v>
+      </c>
+      <c r="I10" s="27">
+        <v>3</v>
+      </c>
+      <c r="J10" s="27">
+        <v>3</v>
+      </c>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27">
+        <v>2</v>
+      </c>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27">
+        <v>8</v>
+      </c>
+      <c r="R10" s="27">
+        <v>1</v>
+      </c>
+      <c r="S10" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="T10" s="50" t="s">
+        <v>247</v>
+      </c>
+      <c r="U10" s="27"/>
+      <c r="V10" s="50" t="s">
+        <v>244</v>
+      </c>
+      <c r="W10" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="X10" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y10" s="27">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA10" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB10" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="AC10" s="27"/>
     </row>
     <row r="11" spans="1:29" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
@@ -2177,151 +2553,223 @@
       <c r="D11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="29"/>
-    </row>
-    <row r="12" spans="1:29" ht="66.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
+      <c r="E11" s="27">
+        <v>13</v>
+      </c>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27">
+        <v>6</v>
+      </c>
+      <c r="J11" s="27">
+        <v>1</v>
+      </c>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27">
+        <v>3</v>
+      </c>
+      <c r="S11" s="27">
+        <v>4</v>
+      </c>
+      <c r="T11" s="27">
+        <v>20</v>
+      </c>
+      <c r="U11" s="27"/>
+      <c r="V11" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="W11" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="X11" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y11" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z11" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA11" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB11" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="AC11" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="4">
         <v>1910</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
-      <c r="X12" s="34"/>
-      <c r="Y12" s="34"/>
-      <c r="Z12" s="34"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="34"/>
-      <c r="AC12" s="34"/>
-    </row>
-    <row r="13" spans="1:29" ht="44.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+      <c r="E12" s="27">
+        <v>2</v>
+      </c>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27">
+        <v>1</v>
+      </c>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27">
+        <v>1</v>
+      </c>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="W12" s="27"/>
+      <c r="X12" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y12" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z12" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA12" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="27">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="61">
         <v>1910</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="28"/>
-    </row>
-    <row r="14" spans="1:29" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="E13" s="67">
+        <v>12</v>
+      </c>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63">
+        <v>2</v>
+      </c>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63">
+        <v>4</v>
+      </c>
+      <c r="J13" s="63">
+        <v>3</v>
+      </c>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63">
+        <v>8</v>
+      </c>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63">
+        <v>4</v>
+      </c>
+      <c r="T13" s="67" t="s">
+        <v>271</v>
+      </c>
+      <c r="U13" s="63"/>
+      <c r="V13" s="66" t="s">
+        <v>269</v>
+      </c>
+      <c r="W13" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="X13" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y13" s="63">
+        <v>5</v>
+      </c>
+      <c r="Z13" s="63">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="63"/>
+      <c r="AB13" s="63"/>
+      <c r="AC13" s="64"/>
+    </row>
+    <row r="14" spans="1:29" ht="59.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="11">
         <v>1911</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31"/>
+      <c r="AC14" s="56"/>
     </row>
     <row r="15" spans="1:29" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -2333,34 +2781,34 @@
       <c r="D15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
-      <c r="Y15" s="29"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="29"/>
-      <c r="AB15" s="29"/>
-      <c r="AC15" s="30"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="28"/>
     </row>
     <row r="16" spans="1:29" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -2372,70 +2820,70 @@
       <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="30"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="28"/>
     </row>
     <row r="17" spans="1:29" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>1914</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="31"/>
-      <c r="AC17" s="32"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="29"/>
+      <c r="AC17" s="30"/>
     </row>
     <row r="18" spans="1:29" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2545,12 +2993,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -2582,191 +3030,191 @@
       <c r="AG1" s="3"/>
     </row>
     <row r="2" spans="1:33" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="I2" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="J2" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="K2" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="L2" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="M2" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="N2" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="O2" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="P2" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="Q2" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="R2" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="47" t="s">
+      <c r="S2" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="47" t="s">
+      <c r="T2" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="R2" s="47" t="s">
+      <c r="U2" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="S2" s="47" t="s">
+      <c r="V2" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="T2" s="47" t="s">
+      <c r="W2" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="U2" s="47" t="s">
+      <c r="X2" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="V2" s="47" t="s">
+      <c r="Y2" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="W2" s="47" t="s">
+      <c r="Z2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="X2" s="47" t="s">
+      <c r="AA2" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="AB2" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="47" t="s">
+      <c r="AC2" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="AA2" s="47" t="s">
+      <c r="AD2" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="AB2" s="47" t="s">
+      <c r="AE2" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="AC2" s="47" t="s">
+      <c r="AF2" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="AD2" s="47" t="s">
+      <c r="AG2" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="AE2" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF2" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG2" s="49" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="3" spans="1:33" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <v>1900</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25">
         <v>5</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27">
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25">
         <v>3</v>
       </c>
-      <c r="K3" s="27">
-        <v>1</v>
-      </c>
-      <c r="L3" s="60">
+      <c r="K3" s="25">
+        <v>1</v>
+      </c>
+      <c r="L3" s="48">
         <v>16</v>
       </c>
-      <c r="M3" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="N3" s="27"/>
-      <c r="O3" s="60" t="s">
-        <v>149</v>
-      </c>
-      <c r="P3" s="27">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27">
-        <v>1</v>
-      </c>
-      <c r="S3" s="27">
+      <c r="M3" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="N3" s="25"/>
+      <c r="O3" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="P3" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25">
+        <v>1</v>
+      </c>
+      <c r="S3" s="25">
         <v>4</v>
       </c>
-      <c r="T3" s="27">
+      <c r="T3" s="25">
         <v>4</v>
       </c>
-      <c r="U3" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="V3" s="60" t="s">
-        <v>146</v>
-      </c>
-      <c r="W3" s="27">
+      <c r="U3" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="V3" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="W3" s="25">
         <v>6</v>
       </c>
-      <c r="X3" s="27" t="s">
+      <c r="X3" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25">
+        <v>3</v>
+      </c>
+      <c r="AB3" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27">
-        <v>3</v>
-      </c>
-      <c r="AB3" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC3" s="27">
+      <c r="AC3" s="25">
         <v>4</v>
       </c>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG3" s="52">
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG3" s="40">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -2778,62 +3226,62 @@
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29" t="s">
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="L4" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="M4" s="27">
+        <v>4</v>
+      </c>
+      <c r="N4" s="27"/>
+      <c r="O4" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="P4" s="27">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="27">
+        <v>1</v>
+      </c>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27">
+        <v>1</v>
+      </c>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="L4" s="62" t="s">
-        <v>165</v>
-      </c>
-      <c r="M4" s="29">
-        <v>4</v>
-      </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="62" t="s">
-        <v>166</v>
-      </c>
-      <c r="P4" s="29">
+      <c r="W4" s="27">
+        <v>6</v>
+      </c>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27">
         <v>2</v>
       </c>
-      <c r="Q4" s="29">
-        <v>1</v>
-      </c>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29">
-        <v>1</v>
-      </c>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="W4" s="29">
-        <v>6</v>
-      </c>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29">
-        <v>3</v>
-      </c>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29">
-        <v>2</v>
-      </c>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="54"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="42"/>
     </row>
     <row r="5" spans="1:33" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -2845,70 +3293,70 @@
       <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="L5" s="62" t="s">
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="L5" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="M5" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="N5" s="27">
+        <v>1</v>
+      </c>
+      <c r="O5" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="M5" s="62" t="s">
-        <v>178</v>
-      </c>
-      <c r="N5" s="29">
-        <v>1</v>
-      </c>
-      <c r="O5" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="P5" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29">
-        <v>1</v>
-      </c>
-      <c r="S5" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="T5" s="29">
+      <c r="P5" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27">
+        <v>1</v>
+      </c>
+      <c r="S5" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="T5" s="27">
         <v>9</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="27">
         <v>2</v>
       </c>
-      <c r="V5" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="W5" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29">
+      <c r="V5" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="W5" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27">
         <v>2</v>
       </c>
-      <c r="AC5" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="AG5" s="66">
+      <c r="AC5" s="27">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="AG5" s="52">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -2920,199 +3368,233 @@
       <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>3</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29">
-        <v>1</v>
-      </c>
-      <c r="K6" s="29">
+      <c r="I6" s="27"/>
+      <c r="J6" s="27">
+        <v>1</v>
+      </c>
+      <c r="K6" s="27">
         <v>3</v>
       </c>
-      <c r="L6" s="62" t="s">
+      <c r="L6" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="M6" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="N6" s="27">
+        <v>2</v>
+      </c>
+      <c r="O6" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="P6" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27">
+        <v>1</v>
+      </c>
+      <c r="S6" s="27"/>
+      <c r="T6" s="50">
+        <v>10</v>
+      </c>
+      <c r="U6" s="27">
+        <v>2</v>
+      </c>
+      <c r="V6" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="W6" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="X6" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="M6" s="29" t="s">
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="50">
+        <v>9</v>
+      </c>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="N6" s="29">
+      <c r="AG6" s="42"/>
+    </row>
+    <row r="7" spans="1:33" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20">
+        <v>1905</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="53">
+        <v>10</v>
+      </c>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29">
+        <v>1</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L7" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="M7" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="N7" s="29"/>
+      <c r="O7" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="P7" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q7" s="29">
+        <v>5</v>
+      </c>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29">
+        <v>1</v>
+      </c>
+      <c r="T7" s="29">
+        <v>9</v>
+      </c>
+      <c r="U7" s="29">
+        <v>3</v>
+      </c>
+      <c r="V7" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="W7" s="29">
+        <v>3</v>
+      </c>
+      <c r="X7" s="29">
         <v>2</v>
       </c>
-      <c r="O6" s="62" t="s">
-        <v>189</v>
-      </c>
-      <c r="P6" s="62" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29">
-        <v>1</v>
-      </c>
-      <c r="S6" s="29"/>
-      <c r="T6" s="62">
-        <v>10</v>
-      </c>
-      <c r="U6" s="29">
+      <c r="Y7" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29">
+        <v>8</v>
+      </c>
+      <c r="AC7" s="29">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="29">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="29">
+        <v>6</v>
+      </c>
+      <c r="AF7" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="AG7" s="44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1908</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31">
+        <v>4</v>
+      </c>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31">
+        <v>4</v>
+      </c>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31">
+        <v>4</v>
+      </c>
+      <c r="K8" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="L8" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="M8" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="N8" s="31"/>
+      <c r="O8" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="P8" s="55" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31">
+        <v>5</v>
+      </c>
+      <c r="U8" s="31">
+        <v>1</v>
+      </c>
+      <c r="V8" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="W8" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="X8" s="31">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="31">
+        <v>3</v>
+      </c>
+      <c r="AF8" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="AG8" s="45">
         <v>2</v>
       </c>
-      <c r="V6" s="62" t="s">
-        <v>193</v>
-      </c>
-      <c r="W6" s="62" t="s">
-        <v>184</v>
-      </c>
-      <c r="X6" s="62" t="s">
-        <v>185</v>
-      </c>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="62">
-        <v>9</v>
-      </c>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="AG6" s="54"/>
-    </row>
-    <row r="7" spans="1:33" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="21">
-        <v>1905</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="67">
-        <v>10</v>
-      </c>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31">
-        <v>1</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="L7" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="M7" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="N7" s="31"/>
-      <c r="O7" s="67" t="s">
-        <v>198</v>
-      </c>
-      <c r="P7" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q7" s="31">
-        <v>5</v>
-      </c>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31">
-        <v>1</v>
-      </c>
-      <c r="T7" s="31">
-        <v>9</v>
-      </c>
-      <c r="U7" s="31">
-        <v>3</v>
-      </c>
-      <c r="V7" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="W7" s="31">
-        <v>3</v>
-      </c>
-      <c r="X7" s="31">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="Z7" s="31"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="31">
-        <v>8</v>
-      </c>
-      <c r="AC7" s="31">
-        <v>3</v>
-      </c>
-      <c r="AD7" s="31">
-        <v>3</v>
-      </c>
-      <c r="AE7" s="31">
-        <v>6</v>
-      </c>
-      <c r="AF7" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG7" s="56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="11">
-        <v>1908</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="33"/>
-      <c r="AD8" s="33"/>
-      <c r="AE8" s="33"/>
-      <c r="AF8" s="57"/>
-      <c r="AG8" s="57"/>
     </row>
     <row r="9" spans="1:33" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
@@ -3127,35 +3609,73 @@
       <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="53"/>
-      <c r="AG9" s="53"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27">
+        <v>2</v>
+      </c>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27">
+        <v>1</v>
+      </c>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27">
+        <v>1</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="L9" s="50" t="s">
+        <v>232</v>
+      </c>
+      <c r="M9" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="N9" s="27"/>
+      <c r="O9" s="50" t="s">
+        <v>234</v>
+      </c>
+      <c r="P9" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q9" s="27">
+        <v>4</v>
+      </c>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="T9" s="50">
+        <v>19</v>
+      </c>
+      <c r="U9" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="V9" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="W9" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="X9" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="27">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="27"/>
+      <c r="AD9" s="27"/>
+      <c r="AE9" s="27"/>
+      <c r="AF9" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG9" s="41">
+        <v>6</v>
+      </c>
     </row>
     <row r="10" spans="1:33" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -3170,35 +3690,61 @@
       <c r="D10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="29"/>
-      <c r="AD10" s="29"/>
-      <c r="AE10" s="29"/>
-      <c r="AF10" s="53"/>
-      <c r="AG10" s="53"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27">
+        <v>4</v>
+      </c>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27">
+        <v>2</v>
+      </c>
+      <c r="J10" s="27">
+        <v>3</v>
+      </c>
+      <c r="K10" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="L10" s="50" t="s">
+        <v>242</v>
+      </c>
+      <c r="M10" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="N10" s="27"/>
+      <c r="O10" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27">
+        <v>1</v>
+      </c>
+      <c r="S10" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="T10" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="U10" s="27"/>
+      <c r="V10" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="W10" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="27"/>
+      <c r="AD10" s="27"/>
+      <c r="AE10" s="27"/>
+      <c r="AF10" s="41"/>
+      <c r="AG10" s="41">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:33" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
@@ -3210,38 +3756,66 @@
       <c r="C11" s="4">
         <v>1909</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="29"/>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="53"/>
-      <c r="AG11" s="53"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27">
+        <v>3</v>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27">
+        <v>1</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="L11" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="M11" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="N11" s="27"/>
+      <c r="O11" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="P11" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27">
+        <v>1</v>
+      </c>
+      <c r="S11" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="T11" s="27">
+        <v>5</v>
+      </c>
+      <c r="U11" s="27">
+        <v>2</v>
+      </c>
+      <c r="V11" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="W11" s="50" t="s">
+        <v>251</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="27"/>
+      <c r="AF11" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG11" s="41"/>
     </row>
     <row r="12" spans="1:33" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -3256,124 +3830,184 @@
       <c r="D12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="29"/>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="53"/>
-      <c r="AG12" s="53"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27">
+        <v>1</v>
+      </c>
+      <c r="K12" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="L12" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M12" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="P12" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q12" s="50">
+        <v>12</v>
+      </c>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27">
+        <v>1</v>
+      </c>
+      <c r="W12" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="X12" s="27">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27"/>
+      <c r="AB12" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="27"/>
+      <c r="AD12" s="27"/>
+      <c r="AE12" s="27">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="AG12" s="41">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:33" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="22">
         <v>1910</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-      <c r="AC13" s="34"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="34"/>
-      <c r="AF13" s="58"/>
-      <c r="AG13" s="58"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32">
+        <v>1</v>
+      </c>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32">
+        <v>2</v>
+      </c>
+      <c r="K13" s="32">
+        <v>1</v>
+      </c>
+      <c r="L13" s="65" t="s">
+        <v>266</v>
+      </c>
+      <c r="M13" s="65" t="s">
+        <v>265</v>
+      </c>
+      <c r="N13" s="32"/>
+      <c r="O13" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="P13" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32">
+        <v>4</v>
+      </c>
+      <c r="U13" s="65" t="s">
+        <v>268</v>
+      </c>
+      <c r="V13" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="W13" s="32">
+        <v>4</v>
+      </c>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="32"/>
+      <c r="AE13" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="AG13" s="46">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:33" ht="59.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <v>1911</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="27"/>
-      <c r="AB14" s="27"/>
-      <c r="AC14" s="27"/>
-      <c r="AD14" s="27"/>
-      <c r="AE14" s="27"/>
-      <c r="AF14" s="51"/>
-      <c r="AG14" s="52"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="39"/>
+      <c r="AG14" s="40"/>
     </row>
     <row r="15" spans="1:33" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -3385,38 +4019,38 @@
       <c r="D15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
-      <c r="Y15" s="29"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="29"/>
-      <c r="AB15" s="29"/>
-      <c r="AC15" s="29"/>
-      <c r="AD15" s="29"/>
-      <c r="AE15" s="29"/>
-      <c r="AF15" s="53"/>
-      <c r="AG15" s="54"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="27"/>
+      <c r="AD15" s="27"/>
+      <c r="AE15" s="27"/>
+      <c r="AF15" s="41"/>
+      <c r="AG15" s="42"/>
     </row>
     <row r="16" spans="1:33" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -3428,78 +4062,78 @@
       <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="29"/>
-      <c r="AD16" s="29"/>
-      <c r="AE16" s="29"/>
-      <c r="AF16" s="53"/>
-      <c r="AG16" s="54"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="41"/>
+      <c r="AG16" s="42"/>
     </row>
     <row r="17" spans="1:33" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>1914</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="31"/>
-      <c r="AC17" s="31"/>
-      <c r="AD17" s="31"/>
-      <c r="AE17" s="31"/>
-      <c r="AF17" s="55"/>
-      <c r="AG17" s="56"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="29"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="43"/>
+      <c r="AG17" s="44"/>
     </row>
     <row r="18" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -3571,49 +4205,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F33BA8E3-E6BA-400F-BB86-C1363B909757}">
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="79" customWidth="1"/>
     <col min="2" max="2" width="37.33203125" customWidth="1"/>
     <col min="3" max="3" width="26.88671875" customWidth="1"/>
     <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="43.21875" customWidth="1"/>
-    <col min="6" max="6" width="25.77734375" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" customWidth="1"/>
-    <col min="8" max="8" width="24.21875" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="30.21875" customWidth="1"/>
-    <col min="15" max="15" width="24.44140625" customWidth="1"/>
-    <col min="16" max="16" width="20.21875" customWidth="1"/>
-    <col min="17" max="17" width="27.77734375" customWidth="1"/>
-    <col min="18" max="18" width="20.21875" customWidth="1"/>
-    <col min="19" max="19" width="21.109375" customWidth="1"/>
-    <col min="20" max="20" width="14.77734375" customWidth="1"/>
-    <col min="21" max="21" width="19.44140625" customWidth="1"/>
-    <col min="22" max="22" width="17.5546875" customWidth="1"/>
-    <col min="23" max="23" width="21.44140625" customWidth="1"/>
-    <col min="24" max="24" width="22.77734375" customWidth="1"/>
-    <col min="25" max="25" width="16.33203125" customWidth="1"/>
-    <col min="26" max="26" width="14.44140625" customWidth="1"/>
-    <col min="27" max="27" width="16.44140625" customWidth="1"/>
-    <col min="28" max="28" width="17.44140625" customWidth="1"/>
-    <col min="29" max="29" width="16.33203125" customWidth="1"/>
-    <col min="30" max="30" width="13.33203125" customWidth="1"/>
-    <col min="31" max="31" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24.21875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" customWidth="1"/>
+    <col min="12" max="12" width="25.77734375" customWidth="1"/>
+    <col min="13" max="13" width="30.21875" customWidth="1"/>
+    <col min="14" max="14" width="24.44140625" customWidth="1"/>
+    <col min="15" max="15" width="20.21875" customWidth="1"/>
+    <col min="16" max="16" width="27.77734375" customWidth="1"/>
+    <col min="17" max="17" width="20.21875" customWidth="1"/>
+    <col min="18" max="18" width="21.109375" customWidth="1"/>
+    <col min="19" max="19" width="14.77734375" customWidth="1"/>
+    <col min="20" max="20" width="19.44140625" customWidth="1"/>
+    <col min="21" max="21" width="17.5546875" customWidth="1"/>
+    <col min="22" max="22" width="21.44140625" customWidth="1"/>
+    <col min="23" max="23" width="22.77734375" customWidth="1"/>
+    <col min="24" max="24" width="16.33203125" customWidth="1"/>
+    <col min="25" max="25" width="14.44140625" customWidth="1"/>
+    <col min="26" max="26" width="16.44140625" customWidth="1"/>
+    <col min="27" max="27" width="17.44140625" customWidth="1"/>
+    <col min="28" max="28" width="16.33203125" customWidth="1"/>
+    <col min="29" max="29" width="13.33203125" customWidth="1"/>
+    <col min="30" max="30" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -3627,63 +4260,60 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-    </row>
-    <row r="2" spans="1:31" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+    </row>
+    <row r="2" spans="1:30" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="38" t="s">
+      <c r="E2" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="I2" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="J2" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="K2" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="L2" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="M2" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="N2" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="O2" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="P2" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="Q2" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="P2" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q2" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="R2" s="47" t="s">
-        <v>106</v>
-      </c>
+      <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -3696,43 +4326,42 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-    </row>
-    <row r="3" spans="1:31" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+    </row>
+    <row r="3" spans="1:30" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <v>1900</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27">
-        <v>1</v>
-      </c>
-      <c r="I3" s="27"/>
-      <c r="J3" s="63">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="51">
         <v>7</v>
       </c>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27">
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25">
         <v>2</v>
       </c>
-      <c r="Q3" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="R3" s="28"/>
+      <c r="P3" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -3745,10 +4374,9 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-    </row>
-    <row r="4" spans="1:31" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+    </row>
+    <row r="4" spans="1:30" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -3760,30 +4388,30 @@
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29">
-        <v>1</v>
-      </c>
-      <c r="G4" s="62">
+      <c r="E4" s="27">
+        <v>1</v>
+      </c>
+      <c r="F4" s="50">
         <v>4</v>
       </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="61">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="49">
         <v>4</v>
       </c>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29">
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27">
         <v>2</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="P4" s="27">
         <v>2</v>
       </c>
-      <c r="R4" s="30"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -3796,10 +4424,9 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-    </row>
-    <row r="5" spans="1:31" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+    </row>
+    <row r="5" spans="1:30" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -3811,24 +4438,24 @@
       <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29">
-        <v>1</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29">
-        <v>1</v>
-      </c>
-      <c r="R5" s="30"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27">
+        <v>1</v>
+      </c>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
@@ -3841,10 +4468,9 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-    </row>
-    <row r="6" spans="1:31" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+    </row>
+    <row r="6" spans="1:30" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -3856,32 +4482,32 @@
       <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="62">
+      <c r="E6" s="50">
         <v>5</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29">
-        <v>1</v>
-      </c>
-      <c r="J6" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="62" t="s">
-        <v>183</v>
-      </c>
-      <c r="R6" s="30">
-        <v>1</v>
-      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
+        <v>1</v>
+      </c>
+      <c r="I6" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27">
+        <v>1</v>
+      </c>
+      <c r="P6" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q6" s="28">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
@@ -3894,43 +4520,46 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-    </row>
-    <row r="7" spans="1:31" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
+    </row>
+    <row r="7" spans="1:30" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <v>1905</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31">
+      <c r="E7" s="29">
+        <v>1</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29">
+        <v>1</v>
+      </c>
+      <c r="I7" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29">
         <v>8</v>
       </c>
-      <c r="Q7" s="67" t="s">
-        <v>197</v>
-      </c>
-      <c r="R7" s="32">
+      <c r="P7" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q7" s="30">
         <v>3</v>
       </c>
+      <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -3943,35 +4572,42 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-    </row>
-    <row r="8" spans="1:31" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    </row>
+    <row r="8" spans="1:30" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>1908</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
+      <c r="E8" s="31">
+        <v>1</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31">
+        <v>1</v>
+      </c>
+      <c r="P8" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -3984,9 +4620,8 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-    </row>
-    <row r="9" spans="1:31" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:30" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -3999,20 +4634,32 @@
       <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27">
+        <v>1</v>
+      </c>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27">
+        <v>2</v>
+      </c>
+      <c r="O9" s="27">
+        <v>6</v>
+      </c>
+      <c r="P9" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q9" s="27">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -4025,9 +4672,8 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-    </row>
-    <row r="10" spans="1:31" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:30" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
@@ -4040,20 +4686,24 @@
       <c r="D10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27">
+        <v>1</v>
+      </c>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
@@ -4066,9 +4716,8 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-    </row>
-    <row r="11" spans="1:31" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:30" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -4078,23 +4727,27 @@
       <c r="C11" s="4">
         <v>1909</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27">
+        <v>5</v>
+      </c>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
@@ -4107,9 +4760,8 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-    </row>
-    <row r="12" spans="1:31" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:30" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -4122,20 +4774,26 @@
       <c r="D12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27">
+        <v>1</v>
+      </c>
+      <c r="P12" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
@@ -4148,35 +4806,40 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-    </row>
-    <row r="13" spans="1:31" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="35" t="s">
+    </row>
+    <row r="13" spans="1:30" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="22">
         <v>1910</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32">
+        <v>1</v>
+      </c>
+      <c r="P13" s="32">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
@@ -4189,35 +4852,34 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-    </row>
-    <row r="14" spans="1:31" ht="59.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+    </row>
+    <row r="14" spans="1:30" ht="59.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <v>1911</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="28"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -4230,10 +4892,9 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-    </row>
-    <row r="15" spans="1:31" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+    </row>
+    <row r="15" spans="1:30" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -4245,20 +4906,20 @@
       <c r="D15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="30"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -4271,10 +4932,9 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-    </row>
-    <row r="16" spans="1:31" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+    </row>
+    <row r="16" spans="1:30" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -4286,20 +4946,20 @@
       <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="30"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -4312,35 +4972,34 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-    </row>
-    <row r="17" spans="1:31" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
+    </row>
+    <row r="17" spans="1:30" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>1914</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="32"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -4353,9 +5012,8 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-    </row>
-    <row r="18" spans="1:31" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="18" spans="1:30" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -4424,49 +5082,48 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87279E7-DDCD-45EF-A8ED-4BE8202D6AE8}">
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="79" customWidth="1"/>
     <col min="2" max="2" width="37.33203125" customWidth="1"/>
     <col min="3" max="3" width="26.88671875" customWidth="1"/>
     <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="43.21875" customWidth="1"/>
-    <col min="6" max="6" width="25.77734375" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" customWidth="1"/>
-    <col min="8" max="8" width="24.21875" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" customWidth="1"/>
-    <col min="11" max="11" width="19.33203125" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="30.21875" customWidth="1"/>
-    <col min="15" max="15" width="24.44140625" customWidth="1"/>
-    <col min="16" max="16" width="20.21875" customWidth="1"/>
-    <col min="17" max="17" width="27.77734375" customWidth="1"/>
-    <col min="18" max="18" width="20.21875" customWidth="1"/>
-    <col min="19" max="19" width="21.109375" customWidth="1"/>
-    <col min="20" max="20" width="14.77734375" customWidth="1"/>
-    <col min="21" max="21" width="19.44140625" customWidth="1"/>
-    <col min="22" max="22" width="17.5546875" customWidth="1"/>
-    <col min="23" max="23" width="21.44140625" customWidth="1"/>
-    <col min="24" max="24" width="22.77734375" customWidth="1"/>
-    <col min="25" max="25" width="16.33203125" customWidth="1"/>
-    <col min="26" max="26" width="14.44140625" customWidth="1"/>
-    <col min="27" max="27" width="16.44140625" customWidth="1"/>
-    <col min="28" max="28" width="17.44140625" customWidth="1"/>
-    <col min="29" max="29" width="16.33203125" customWidth="1"/>
-    <col min="30" max="30" width="13.33203125" customWidth="1"/>
-    <col min="31" max="31" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24.21875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" customWidth="1"/>
+    <col min="12" max="12" width="25.77734375" customWidth="1"/>
+    <col min="13" max="13" width="30.21875" customWidth="1"/>
+    <col min="14" max="14" width="24.44140625" customWidth="1"/>
+    <col min="15" max="15" width="20.21875" customWidth="1"/>
+    <col min="16" max="16" width="27.77734375" customWidth="1"/>
+    <col min="17" max="17" width="20.21875" customWidth="1"/>
+    <col min="18" max="18" width="21.109375" customWidth="1"/>
+    <col min="19" max="19" width="14.77734375" customWidth="1"/>
+    <col min="20" max="20" width="19.44140625" customWidth="1"/>
+    <col min="21" max="21" width="17.5546875" customWidth="1"/>
+    <col min="22" max="22" width="21.44140625" customWidth="1"/>
+    <col min="23" max="23" width="22.77734375" customWidth="1"/>
+    <col min="24" max="24" width="16.33203125" customWidth="1"/>
+    <col min="25" max="25" width="14.44140625" customWidth="1"/>
+    <col min="26" max="26" width="16.44140625" customWidth="1"/>
+    <col min="27" max="27" width="17.44140625" customWidth="1"/>
+    <col min="28" max="28" width="16.33203125" customWidth="1"/>
+    <col min="29" max="29" width="13.33203125" customWidth="1"/>
+    <col min="30" max="30" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -4478,57 +5135,54 @@
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-    </row>
-    <row r="2" spans="1:31" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+    </row>
+    <row r="2" spans="1:30" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="38" t="s">
+      <c r="E2" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="I2" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="J2" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="K2" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="L2" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="M2" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="N2" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="O2" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="N2" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="O2" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="P2" s="38" t="s">
-        <v>117</v>
-      </c>
+      <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -4543,43 +5197,42 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-    </row>
-    <row r="3" spans="1:31" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+    </row>
+    <row r="3" spans="1:30" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <v>1900</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="64" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="L3" s="25">
+        <v>1</v>
+      </c>
+      <c r="M3" s="25">
+        <v>1</v>
+      </c>
+      <c r="N3" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="M3" s="39">
-        <v>1</v>
-      </c>
-      <c r="N3" s="39">
-        <v>1</v>
-      </c>
-      <c r="O3" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="P3" s="40"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -4594,10 +5247,9 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-    </row>
-    <row r="4" spans="1:31" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+    </row>
+    <row r="4" spans="1:30" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -4609,32 +5261,32 @@
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41">
-        <v>1</v>
-      </c>
-      <c r="G4" s="41">
-        <v>1</v>
-      </c>
-      <c r="H4" s="41">
-        <v>1</v>
-      </c>
-      <c r="I4" s="65" t="s">
+      <c r="E4" s="27">
+        <v>1</v>
+      </c>
+      <c r="F4" s="27">
+        <v>1</v>
+      </c>
+      <c r="G4" s="27">
+        <v>1</v>
+      </c>
+      <c r="H4" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41" t="s">
-        <v>167</v>
-      </c>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41">
-        <v>1</v>
-      </c>
-      <c r="O4" s="41">
-        <v>1</v>
-      </c>
-      <c r="P4" s="42"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27">
+        <v>1</v>
+      </c>
+      <c r="N4" s="27">
+        <v>1</v>
+      </c>
+      <c r="O4" s="28"/>
+      <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
@@ -4649,10 +5301,9 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-    </row>
-    <row r="5" spans="1:31" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+    </row>
+    <row r="5" spans="1:30" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -4664,26 +5315,26 @@
       <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="65" t="s">
-        <v>179</v>
-      </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="M5" s="41"/>
-      <c r="N5" s="65" t="s">
-        <v>180</v>
-      </c>
-      <c r="O5" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="P5" s="42"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="L5" s="27"/>
+      <c r="M5" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="N5" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="O5" s="28"/>
+      <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -4698,10 +5349,9 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-    </row>
-    <row r="6" spans="1:31" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+    </row>
+    <row r="6" spans="1:30" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -4713,26 +5363,26 @@
       <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="65" t="s">
-        <v>186</v>
-      </c>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27">
         <v>4</v>
       </c>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27">
         <v>7</v>
       </c>
-      <c r="O6" s="65" t="s">
-        <v>187</v>
-      </c>
-      <c r="P6" s="42"/>
+      <c r="N6" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="O6" s="28"/>
+      <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -4747,43 +5397,42 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-    </row>
-    <row r="7" spans="1:31" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
+    </row>
+    <row r="7" spans="1:30" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <v>1905</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="M7" s="43">
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="L7" s="29">
         <v>7</v>
       </c>
-      <c r="N7" s="43">
+      <c r="M7" s="29">
         <v>4</v>
       </c>
-      <c r="O7" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="P7" s="44"/>
+      <c r="N7" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="O7" s="30"/>
+      <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -4798,33 +5447,40 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-    </row>
-    <row r="8" spans="1:31" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    </row>
+    <row r="8" spans="1:30" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>1908</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31">
+        <v>5</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="O8" s="31"/>
+      <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -4839,9 +5495,8 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-    </row>
-    <row r="9" spans="1:31" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:30" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -4854,18 +5509,26 @@
       <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="N9" s="50" t="s">
+        <v>235</v>
+      </c>
+      <c r="O9" s="27"/>
+      <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -4880,9 +5543,8 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-    </row>
-    <row r="10" spans="1:31" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:30" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
@@ -4895,18 +5557,22 @@
       <c r="D10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27">
+        <v>1</v>
+      </c>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -4921,9 +5587,8 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-    </row>
-    <row r="11" spans="1:31" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:30" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -4933,21 +5598,27 @@
       <c r="C11" s="4">
         <v>1909</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27">
+        <v>5</v>
+      </c>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27">
+        <v>9</v>
+      </c>
+      <c r="O11" s="27"/>
+      <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -4962,9 +5633,8 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-    </row>
-    <row r="12" spans="1:31" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:30" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -4977,18 +5647,28 @@
       <c r="D12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="N12" s="27">
+        <v>1</v>
+      </c>
+      <c r="O12" s="27">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -5003,33 +5683,38 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-    </row>
-    <row r="13" spans="1:31" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="35" t="s">
+    </row>
+    <row r="13" spans="1:30" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="22">
         <v>1910</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="O13" s="32"/>
+      <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -5044,33 +5729,32 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-    </row>
-    <row r="14" spans="1:31" ht="59.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+    </row>
+    <row r="14" spans="1:30" ht="59.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <v>1911</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="40"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -5085,10 +5769,9 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-    </row>
-    <row r="15" spans="1:31" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+    </row>
+    <row r="15" spans="1:30" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -5100,18 +5783,18 @@
       <c r="D15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="42"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -5126,10 +5809,9 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-    </row>
-    <row r="16" spans="1:31" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+    </row>
+    <row r="16" spans="1:30" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -5141,18 +5823,18 @@
       <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="42"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -5167,33 +5849,32 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-    </row>
-    <row r="17" spans="1:31" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
+    </row>
+    <row r="17" spans="1:30" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>1914</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="44"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -5208,9 +5889,8 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-    </row>
-    <row r="18" spans="1:31" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="18" spans="1:30" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -5279,49 +5959,48 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63946A57-726F-40DF-AD6C-B26CCBF049DF}">
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="79" customWidth="1"/>
     <col min="2" max="2" width="37.33203125" customWidth="1"/>
     <col min="3" max="3" width="26.88671875" customWidth="1"/>
     <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="43.21875" customWidth="1"/>
-    <col min="6" max="6" width="25.77734375" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" customWidth="1"/>
-    <col min="8" max="8" width="24.21875" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="30.21875" customWidth="1"/>
-    <col min="15" max="15" width="24.44140625" customWidth="1"/>
-    <col min="16" max="16" width="20.21875" customWidth="1"/>
-    <col min="17" max="17" width="27.77734375" customWidth="1"/>
-    <col min="18" max="18" width="20.21875" customWidth="1"/>
-    <col min="19" max="19" width="21.109375" customWidth="1"/>
-    <col min="20" max="20" width="14.77734375" customWidth="1"/>
-    <col min="21" max="21" width="19.44140625" customWidth="1"/>
-    <col min="22" max="22" width="17.5546875" customWidth="1"/>
-    <col min="23" max="23" width="21.44140625" customWidth="1"/>
-    <col min="24" max="24" width="22.77734375" customWidth="1"/>
-    <col min="25" max="25" width="16.33203125" customWidth="1"/>
-    <col min="26" max="26" width="14.44140625" customWidth="1"/>
-    <col min="27" max="27" width="16.44140625" customWidth="1"/>
-    <col min="28" max="28" width="17.44140625" customWidth="1"/>
-    <col min="29" max="29" width="16.33203125" customWidth="1"/>
-    <col min="30" max="30" width="13.33203125" customWidth="1"/>
-    <col min="31" max="31" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24.21875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" customWidth="1"/>
+    <col min="12" max="12" width="25.77734375" customWidth="1"/>
+    <col min="13" max="13" width="30.21875" customWidth="1"/>
+    <col min="14" max="14" width="24.44140625" customWidth="1"/>
+    <col min="15" max="15" width="20.21875" customWidth="1"/>
+    <col min="16" max="16" width="27.77734375" customWidth="1"/>
+    <col min="17" max="17" width="20.21875" customWidth="1"/>
+    <col min="18" max="18" width="21.109375" customWidth="1"/>
+    <col min="19" max="19" width="14.77734375" customWidth="1"/>
+    <col min="20" max="20" width="19.44140625" customWidth="1"/>
+    <col min="21" max="21" width="17.5546875" customWidth="1"/>
+    <col min="22" max="22" width="21.44140625" customWidth="1"/>
+    <col min="23" max="23" width="22.77734375" customWidth="1"/>
+    <col min="24" max="24" width="16.33203125" customWidth="1"/>
+    <col min="25" max="25" width="14.44140625" customWidth="1"/>
+    <col min="26" max="26" width="16.44140625" customWidth="1"/>
+    <col min="27" max="27" width="17.44140625" customWidth="1"/>
+    <col min="28" max="28" width="16.33203125" customWidth="1"/>
+    <col min="29" max="29" width="13.33203125" customWidth="1"/>
+    <col min="30" max="30" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -5345,158 +6024,153 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-    </row>
-    <row r="2" spans="1:31" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+    </row>
+    <row r="2" spans="1:30" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="38" t="s">
+      <c r="E2" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="I2" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="J2" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="K2" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="L2" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="M2" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="N2" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="O2" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="N2" s="38" t="s">
+      <c r="P2" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="O2" s="38" t="s">
+      <c r="Q2" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="P2" s="38" t="s">
+      <c r="R2" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="Q2" s="38" t="s">
+      <c r="S2" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="R2" s="38" t="s">
+      <c r="T2" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="38" t="s">
+      <c r="U2" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="T2" s="38" t="s">
+      <c r="V2" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="U2" s="38" t="s">
+      <c r="W2" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="V2" s="38" t="s">
+      <c r="X2" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="W2" s="38" t="s">
+      <c r="Y2" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="X2" s="38" t="s">
+      <c r="Z2" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="AA2" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="Z2" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA2" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB2" s="38" t="s">
-        <v>140</v>
-      </c>
+      <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-    </row>
-    <row r="3" spans="1:31" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+    </row>
+    <row r="3" spans="1:30" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <v>1900</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25">
         <v>2</v>
       </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="60">
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="48">
         <v>9</v>
       </c>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27">
-        <v>1</v>
-      </c>
-      <c r="T3" s="27">
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25">
+        <v>1</v>
+      </c>
+      <c r="S3" s="25">
         <v>4</v>
       </c>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27">
+      <c r="T3" s="25"/>
+      <c r="U3" s="25">
         <v>9</v>
       </c>
-      <c r="W3" s="27"/>
-      <c r="X3" s="60" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y3" s="60">
+      <c r="V3" s="25"/>
+      <c r="W3" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="X3" s="48">
         <v>11</v>
       </c>
-      <c r="Z3" s="27">
+      <c r="Y3" s="25">
         <v>2</v>
       </c>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="28">
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="26">
         <v>5</v>
       </c>
+      <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-    </row>
-    <row r="4" spans="1:31" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+    </row>
+    <row r="4" spans="1:30" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -5508,46 +6182,45 @@
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29">
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27">
         <v>5</v>
       </c>
-      <c r="W4" s="29"/>
-      <c r="X4" s="62" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y4" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z4" s="29">
+      <c r="V4" s="27"/>
+      <c r="W4" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="X4" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y4" s="27">
         <v>3</v>
       </c>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="30">
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="28">
         <v>4</v>
       </c>
+      <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-    </row>
-    <row r="5" spans="1:31" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+    </row>
+    <row r="5" spans="1:30" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -5559,54 +6232,53 @@
       <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29">
+      <c r="E5" s="27"/>
+      <c r="F5" s="27">
         <v>3</v>
       </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29">
-        <v>1</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29">
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27">
+        <v>1</v>
+      </c>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27">
         <v>3</v>
       </c>
-      <c r="T5" s="29">
+      <c r="S5" s="27">
         <v>4</v>
       </c>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29">
+      <c r="T5" s="27"/>
+      <c r="U5" s="27">
         <v>5</v>
       </c>
-      <c r="W5" s="29"/>
-      <c r="X5" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y5" s="62" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z5" s="29">
+      <c r="V5" s="27"/>
+      <c r="W5" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="X5" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y5" s="27">
         <v>4</v>
       </c>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="30">
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="28">
         <v>7</v>
       </c>
+      <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-    </row>
-    <row r="6" spans="1:31" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+    </row>
+    <row r="6" spans="1:30" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -5618,149 +6290,172 @@
       <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27">
         <v>5</v>
       </c>
-      <c r="M6" s="29">
+      <c r="L6" s="27">
         <v>2</v>
       </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29">
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27">
         <v>5</v>
       </c>
-      <c r="U6" s="29">
-        <v>1</v>
-      </c>
-      <c r="V6" s="29">
+      <c r="T6" s="27">
+        <v>1</v>
+      </c>
+      <c r="U6" s="27">
         <v>5</v>
       </c>
-      <c r="W6" s="29"/>
-      <c r="X6" s="62" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y6" s="29">
+      <c r="V6" s="27"/>
+      <c r="W6" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="X6" s="27">
         <v>6</v>
       </c>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="30">
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="28">
         <v>6</v>
       </c>
+      <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-    </row>
-    <row r="7" spans="1:31" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
+    </row>
+    <row r="7" spans="1:30" ht="54.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <v>1905</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31">
-        <v>1</v>
-      </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31">
+      <c r="E7" s="29"/>
+      <c r="F7" s="29">
+        <v>1</v>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="53">
         <v>9</v>
       </c>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31">
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29">
         <v>3</v>
       </c>
-      <c r="U7" s="31"/>
-      <c r="V7" s="67">
+      <c r="T7" s="29"/>
+      <c r="U7" s="53">
         <v>14</v>
       </c>
-      <c r="W7" s="31"/>
-      <c r="X7" s="67" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y7" s="67">
+      <c r="V7" s="29"/>
+      <c r="W7" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="X7" s="53">
         <v>11</v>
       </c>
-      <c r="Z7" s="67">
+      <c r="Y7" s="53">
         <v>14</v>
       </c>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="32">
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="30">
         <v>3</v>
       </c>
+      <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-    </row>
-    <row r="8" spans="1:31" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    </row>
+    <row r="8" spans="1:30" ht="61.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>1908</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="33"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="55">
+        <v>7</v>
+      </c>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="55">
+        <v>6</v>
+      </c>
+      <c r="J8" s="31">
+        <v>1</v>
+      </c>
+      <c r="K8" s="31">
+        <v>1</v>
+      </c>
+      <c r="L8" s="55">
+        <v>14</v>
+      </c>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31">
+        <v>1</v>
+      </c>
+      <c r="S8" s="31">
+        <v>5</v>
+      </c>
+      <c r="T8" s="31"/>
+      <c r="U8" s="55">
+        <v>15</v>
+      </c>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="X8" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y8" s="55">
+        <v>13</v>
+      </c>
+      <c r="Z8" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="55">
+        <v>24</v>
+      </c>
+      <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-    </row>
-    <row r="9" spans="1:31" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:30" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -5773,35 +6468,44 @@
       <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27">
+        <v>7</v>
+      </c>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27">
+        <v>9</v>
+      </c>
+      <c r="V9" s="27"/>
+      <c r="W9" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="X9" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-    </row>
-    <row r="10" spans="1:31" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:30" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
@@ -5814,35 +6518,54 @@
       <c r="D10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="50">
+        <v>6</v>
+      </c>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27">
+        <v>1</v>
+      </c>
+      <c r="J10" s="27">
+        <v>2</v>
+      </c>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27">
+        <v>3</v>
+      </c>
+      <c r="T10" s="27">
+        <v>1</v>
+      </c>
+      <c r="U10" s="50">
+        <v>10</v>
+      </c>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="X10" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y10" s="27">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="50">
+        <v>19</v>
+      </c>
+      <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-    </row>
-    <row r="11" spans="1:31" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:30" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -5855,35 +6578,46 @@
       <c r="D11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
-      <c r="AB11" s="29"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27">
+        <v>1</v>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="27">
+        <v>10</v>
+      </c>
+      <c r="V11" s="27"/>
+      <c r="W11" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="X11" s="27">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="27">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27">
+        <v>8</v>
+      </c>
+      <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-    </row>
-    <row r="12" spans="1:31" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:30" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -5896,118 +6630,159 @@
       <c r="D12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27">
+        <v>3</v>
+      </c>
+      <c r="G12" s="50">
+        <v>6</v>
+      </c>
+      <c r="H12" s="50">
+        <v>25</v>
+      </c>
+      <c r="I12" s="50">
+        <v>6</v>
+      </c>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="50">
+        <v>6</v>
+      </c>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="50">
+        <v>4</v>
+      </c>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="50">
+        <v>4</v>
+      </c>
+      <c r="R12" s="50">
+        <v>18</v>
+      </c>
+      <c r="S12" s="50">
+        <v>14</v>
+      </c>
+      <c r="T12" s="27"/>
+      <c r="U12" s="50">
+        <v>16</v>
+      </c>
+      <c r="V12" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="W12" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="X12" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y12" s="50">
+        <v>16</v>
+      </c>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27">
+        <v>13</v>
+      </c>
+      <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-    </row>
-    <row r="13" spans="1:31" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="35" t="s">
+    </row>
+    <row r="13" spans="1:30" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="22">
         <v>1910</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32">
+        <v>2</v>
+      </c>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32">
+        <v>1</v>
+      </c>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32">
+        <v>11</v>
+      </c>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32">
+        <v>6</v>
+      </c>
+      <c r="X13" s="32">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="32">
+        <v>3</v>
+      </c>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32">
+        <v>2</v>
+      </c>
+      <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-    </row>
-    <row r="14" spans="1:31" ht="59.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+    </row>
+    <row r="14" spans="1:30" ht="59.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <v>1911</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="27"/>
-      <c r="AB14" s="28"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-    </row>
-    <row r="15" spans="1:31" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+    </row>
+    <row r="15" spans="1:30" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -6019,36 +6794,35 @@
       <c r="D15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
-      <c r="Y15" s="29"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="29"/>
-      <c r="AB15" s="30"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-    </row>
-    <row r="16" spans="1:31" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+    </row>
+    <row r="16" spans="1:30" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -6060,76 +6834,74 @@
       <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="30"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-    </row>
-    <row r="17" spans="1:31" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
+    </row>
+    <row r="17" spans="1:30" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>1914</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="32"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="30"/>
+      <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-    </row>
-    <row r="18" spans="1:31" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="18" spans="1:30" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/Relaciones totales libro-patrimonio/LIBRO PATRIMONIO MATERIAL.xlsx
+++ b/Relaciones totales libro-patrimonio/LIBRO PATRIMONIO MATERIAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE958AD1-F272-48A5-89A0-CB72F7D5F769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A30B1D-3040-4141-84B9-D8F18A9B136B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monumentos" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="326">
   <si>
     <t>RELATOS DE VIAJES ANGLOSAJONES (1900-1914)</t>
   </si>
@@ -3056,6 +3056,9 @@
       </rPr>
       <t xml:space="preserve"> (11+1)</t>
     </r>
+  </si>
+  <si>
+    <t>Sacromonte</t>
   </si>
 </sst>
 </file>
@@ -3456,7 +3459,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3674,22 +3677,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3708,8 +3696,20 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3717,14 +3717,11 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4040,38 +4037,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="89" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="90"/>
-      <c r="V1" s="90"/>
-      <c r="W1" s="90"/>
-      <c r="X1" s="90"/>
-      <c r="Y1" s="90"/>
-      <c r="Z1" s="90"/>
-      <c r="AA1" s="90"/>
-      <c r="AB1" s="90"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
     </row>
     <row r="2" spans="1:28" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -5319,7 +5316,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327378CF-D488-4A3A-B664-FD514517477C}">
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AF18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="79" customWidth="1"/>
@@ -5351,47 +5348,48 @@
     <col min="28" max="28" width="16.44140625" customWidth="1"/>
     <col min="29" max="29" width="15" customWidth="1"/>
     <col min="30" max="30" width="12.21875" customWidth="1"/>
-    <col min="31" max="31" width="14.21875" customWidth="1"/>
+    <col min="31" max="32" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+    <row r="1" spans="1:32" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="74" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83" t="s">
         <v>230</v>
       </c>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="75"/>
-      <c r="Z1" s="75"/>
-      <c r="AA1" s="75"/>
-      <c r="AB1" s="75"/>
-      <c r="AC1" s="75"/>
-      <c r="AD1" s="75"/>
-      <c r="AE1" s="75"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="84"/>
+      <c r="AD1" s="84"/>
+      <c r="AE1" s="84"/>
+      <c r="AF1" s="84"/>
     </row>
-    <row r="2" spans="1:31" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -5485,8 +5483,11 @@
       <c r="AE2" s="31" t="s">
         <v>62</v>
       </c>
+      <c r="AF2" s="31" t="s">
+        <v>325</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" ht="38.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="38.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
@@ -5566,8 +5567,9 @@
       </c>
       <c r="AD3" s="23"/>
       <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
     </row>
-    <row r="4" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>8</v>
       </c>
@@ -5633,8 +5635,9 @@
       <c r="AC4" s="24"/>
       <c r="AD4" s="24"/>
       <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
     </row>
-    <row r="5" spans="1:31" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>11</v>
       </c>
@@ -5706,8 +5709,11 @@
         <v>1</v>
       </c>
       <c r="AE5" s="24"/>
+      <c r="AF5" s="24">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>13</v>
       </c>
@@ -5783,8 +5789,9 @@
         <v>2</v>
       </c>
       <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
     </row>
-    <row r="7" spans="1:31" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
@@ -5868,8 +5875,9 @@
       <c r="AC7" s="25"/>
       <c r="AD7" s="25"/>
       <c r="AE7" s="25"/>
+      <c r="AF7" s="25"/>
     </row>
-    <row r="8" spans="1:31" ht="39.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" ht="39.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -5943,8 +5951,9 @@
       <c r="AC8" s="26"/>
       <c r="AD8" s="26"/>
       <c r="AE8" s="26"/>
+      <c r="AF8" s="26"/>
     </row>
-    <row r="9" spans="1:31" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -6022,8 +6031,9 @@
       <c r="AC9" s="24"/>
       <c r="AD9" s="24"/>
       <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
     </row>
-    <row r="10" spans="1:31" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -6089,8 +6099,9 @@
       <c r="AE10" s="61">
         <v>2</v>
       </c>
+      <c r="AF10" s="39"/>
     </row>
-    <row r="11" spans="1:31" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -6158,8 +6169,9 @@
       </c>
       <c r="AD11" s="24"/>
       <c r="AE11" s="24"/>
+      <c r="AF11" s="24"/>
     </row>
-    <row r="12" spans="1:31" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -6229,8 +6241,9 @@
       <c r="AC12" s="24"/>
       <c r="AD12" s="24"/>
       <c r="AE12" s="24"/>
+      <c r="AF12" s="24"/>
     </row>
-    <row r="13" spans="1:31" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="28" t="s">
         <v>27</v>
       </c>
@@ -6300,8 +6313,9 @@
       <c r="AC13" s="27"/>
       <c r="AD13" s="27"/>
       <c r="AE13" s="27"/>
+      <c r="AF13" s="27"/>
     </row>
-    <row r="14" spans="1:31" ht="41.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" ht="41.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>30</v>
       </c>
@@ -6379,8 +6393,9 @@
       <c r="AC14" s="23"/>
       <c r="AD14" s="23"/>
       <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:31" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>32</v>
       </c>
@@ -6448,8 +6463,11 @@
       <c r="AC15" s="24"/>
       <c r="AD15" s="24"/>
       <c r="AE15" s="24"/>
+      <c r="AF15" s="24">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>34</v>
       </c>
@@ -6531,8 +6549,9 @@
       </c>
       <c r="AD16" s="24"/>
       <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
     </row>
-    <row r="17" spans="1:31" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
         <v>36</v>
       </c>
@@ -6608,8 +6627,9 @@
       <c r="AC17" s="25"/>
       <c r="AD17" s="25"/>
       <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
     </row>
-    <row r="18" spans="1:31" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="D18" s="66" t="s">
         <v>158</v>
       </c>
@@ -6692,13 +6712,16 @@
         <v>3</v>
       </c>
       <c r="AE18" s="58">
+        <v>2</v>
+      </c>
+      <c r="AF18" s="58">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:AE1"/>
+    <mergeCell ref="E1:AF1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A10 A12 A14:A17">
     <cfRule type="colorScale" priority="1">
@@ -6797,23 +6820,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="86" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="85" t="s">
         <v>276</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
     </row>
     <row r="2" spans="1:26" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -7071,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="25"/>
-      <c r="J7" s="88">
+      <c r="J7" s="81">
         <v>3</v>
       </c>
       <c r="K7" s="25">
@@ -7167,7 +7190,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="24"/>
-      <c r="L9" s="80">
+      <c r="L9" s="75">
         <v>2</v>
       </c>
       <c r="M9" s="24"/>
@@ -7416,7 +7439,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="24"/>
-      <c r="I15" s="80">
+      <c r="I15" s="75">
         <v>3</v>
       </c>
       <c r="J15" s="49"/>
@@ -7503,7 +7526,7 @@
       <c r="G17" s="27"/>
       <c r="H17" s="27"/>
       <c r="I17" s="27"/>
-      <c r="J17" s="84"/>
+      <c r="J17" s="79"/>
       <c r="K17" s="24"/>
       <c r="L17" s="27"/>
       <c r="M17" s="27"/>
@@ -7522,10 +7545,10 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="28.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="76"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="79" t="s">
+      <c r="A18" s="73"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="74" t="s">
         <v>275</v>
       </c>
       <c r="E18" s="55">
@@ -7660,25 +7683,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="77" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="87" t="s">
         <v>285</v>
       </c>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
     </row>
     <row r="2" spans="1:30" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -8334,7 +8357,7 @@
       </c>
       <c r="J14" s="23"/>
       <c r="K14" s="23"/>
-      <c r="L14" s="83">
+      <c r="L14" s="78">
         <v>2</v>
       </c>
       <c r="M14" s="23"/>
@@ -8494,7 +8517,7 @@
       <c r="K17" s="27">
         <v>1</v>
       </c>
-      <c r="L17" s="84"/>
+      <c r="L17" s="79"/>
       <c r="M17" s="24"/>
       <c r="N17" s="27"/>
       <c r="O17" s="27"/>
@@ -8515,10 +8538,10 @@
       <c r="AD17" s="1"/>
     </row>
     <row r="18" spans="1:30" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="76"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="79" t="s">
+      <c r="A18" s="73"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="74" t="s">
         <v>284</v>
       </c>
       <c r="E18" s="55">
@@ -8653,32 +8676,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="77" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="85"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="80"/>
     </row>
     <row r="2" spans="1:25" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -9496,7 +9519,7 @@
       <c r="D17" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="81" t="s">
+      <c r="E17" s="76" t="s">
         <v>319</v>
       </c>
       <c r="F17" s="67">
@@ -9505,7 +9528,7 @@
       <c r="G17" s="67">
         <v>14</v>
       </c>
-      <c r="H17" s="84">
+      <c r="H17" s="79">
         <v>2</v>
       </c>
       <c r="I17" s="24"/>
@@ -9531,10 +9554,10 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" spans="1:25" ht="32.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="76"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="79" t="s">
+      <c r="A18" s="73"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="74" t="s">
         <v>284</v>
       </c>
       <c r="E18" s="55">

--- a/Relaciones totales libro-patrimonio/LIBRO PATRIMONIO MATERIAL.xlsx
+++ b/Relaciones totales libro-patrimonio/LIBRO PATRIMONIO MATERIAL.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C82BAEB-9B94-4360-A279-6F9861EF08C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AF44D2-BF0D-4C39-9DD1-9E2C5846217D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monumentos" sheetId="1" r:id="rId1"/>
     <sheet name="espacios públicos" sheetId="2" r:id="rId2"/>
-    <sheet name="comida y bebida" sheetId="3" r:id="rId3"/>
+    <sheet name="Consumo" sheetId="3" r:id="rId3"/>
     <sheet name="camino y viaje" sheetId="4" r:id="rId4"/>
     <sheet name="Espacios naturales" sheetId="5" r:id="rId5"/>
   </sheets>
@@ -2399,9 +2399,6 @@
     <t>total</t>
   </si>
   <si>
-    <t>COMIDA Y IOBJETOS RELACIONADOS CON LA COMIDA Y BEBIBDA</t>
-  </si>
-  <si>
     <r>
       <t>7</t>
     </r>
@@ -3210,6 +3207,9 @@
       </rPr>
       <t xml:space="preserve"> 2271</t>
     </r>
+  </si>
+  <si>
+    <t>CONSUMO: OBJETOS RELACIONADOS CON LA COMIDA Y BEBIBDA</t>
   </si>
 </sst>
 </file>
@@ -3853,10 +3853,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3868,10 +3868,10 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4304,7 +4304,7 @@
         <v>47</v>
       </c>
       <c r="AB2" s="31" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="38.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -5400,7 +5400,7 @@
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="J21" s="84" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K21" s="84"/>
       <c r="L21" s="84"/>
@@ -5668,7 +5668,7 @@
         <v>62</v>
       </c>
       <c r="AF2" s="31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="38.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -6904,7 +6904,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="M20" s="84" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N20" s="84"/>
       <c r="O20" s="84"/>
@@ -7043,17 +7043,17 @@
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
       <c r="D1" s="81"/>
-      <c r="E1" s="87" t="s">
-        <v>276</v>
-      </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
+      <c r="E1" s="82" t="s">
+        <v>334</v>
+      </c>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
     </row>
     <row r="2" spans="1:26" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -7123,7 +7123,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F3" s="40">
         <v>7</v>
@@ -7251,7 +7251,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="61" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F6" s="61" t="s">
         <v>237</v>
@@ -7299,7 +7299,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F7" s="59" t="s">
         <v>240</v>
@@ -7350,7 +7350,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="60" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G8" s="26">
         <v>1</v>
@@ -7394,7 +7394,7 @@
         <v>146</v>
       </c>
       <c r="F9" s="61" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G9" s="61">
         <v>6</v>
@@ -7603,7 +7603,7 @@
         <v>7</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F14" s="62">
         <v>9</v>
@@ -7691,7 +7691,7 @@
         <v>7</v>
       </c>
       <c r="E16" s="61" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F16" s="61" t="s">
         <v>273</v>
@@ -7798,7 +7798,7 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="E20" s="84" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F20" s="84"/>
       <c r="G20" s="84"/>
@@ -7941,20 +7941,20 @@
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
       <c r="D1" s="81"/>
-      <c r="E1" s="82" t="s">
-        <v>285</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
+      <c r="E1" s="87" t="s">
+        <v>284</v>
+      </c>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
     </row>
     <row r="2" spans="1:31" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -7976,16 +7976,16 @@
         <v>102</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I2" s="31" t="s">
         <v>101</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K2" s="31" t="s">
         <v>100</v>
@@ -8035,13 +8035,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F3" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G3" s="62" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H3" s="62">
         <v>15</v>
@@ -8092,7 +8092,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="61" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F4" s="24">
         <v>1</v>
@@ -8149,10 +8149,10 @@
         <v>7</v>
       </c>
       <c r="E5" s="61" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F5" s="61" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G5" s="24">
         <v>6</v>
@@ -8161,7 +8161,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="61" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J5" s="24">
         <v>2</v>
@@ -8204,10 +8204,10 @@
         <v>15</v>
       </c>
       <c r="E6" s="61" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F6" s="61" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G6" s="61">
         <v>14</v>
@@ -8257,10 +8257,10 @@
         <v>7</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F7" s="59" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G7" s="25">
         <v>8</v>
@@ -8318,7 +8318,7 @@
         <v>131</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H8" s="26">
         <v>2</v>
@@ -8367,16 +8367,16 @@
         <v>15</v>
       </c>
       <c r="E9" s="61" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9" s="61" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G9" s="24" t="s">
         <v>124</v>
       </c>
       <c r="H9" s="61" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I9" s="24" t="s">
         <v>133</v>
@@ -8469,7 +8469,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="61" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F11" s="24">
         <v>9</v>
@@ -8626,10 +8626,10 @@
         <v>7</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F14" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G14" s="23" t="s">
         <v>153</v>
@@ -8638,7 +8638,7 @@
         <v>125</v>
       </c>
       <c r="I14" s="62" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J14" s="23">
         <v>7</v>
@@ -8736,16 +8736,16 @@
         <v>7</v>
       </c>
       <c r="E16" s="61" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H16" s="61" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I16" s="24" t="s">
         <v>140</v>
@@ -8791,13 +8791,13 @@
         <v>15</v>
       </c>
       <c r="E17" s="67" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F17" s="67" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G17" s="67" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H17" s="27" t="s">
         <v>126</v>
@@ -8837,7 +8837,7 @@
       <c r="B18" s="73"/>
       <c r="C18" s="73"/>
       <c r="D18" s="74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E18" s="55">
         <v>219</v>
@@ -8878,7 +8878,7 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="G20" s="84" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H20" s="84"/>
       <c r="I20" s="84"/>
@@ -9013,25 +9013,25 @@
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
       <c r="D1" s="81"/>
-      <c r="E1" s="82" t="s">
-        <v>310</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
+      <c r="E1" s="87" t="s">
+        <v>309</v>
+      </c>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
       <c r="V1" s="79"/>
     </row>
     <row r="2" spans="1:25" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9119,7 +9119,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F3" s="62">
         <v>11</v>
@@ -9172,7 +9172,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="61" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F4" s="24" t="s">
         <v>133</v>
@@ -9217,10 +9217,10 @@
         <v>7</v>
       </c>
       <c r="E5" s="61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F5" s="61" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G5" s="24">
         <v>5</v>
@@ -9270,7 +9270,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="61" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6" s="24">
         <v>6</v>
@@ -9321,7 +9321,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F7" s="59">
         <v>11</v>
@@ -9372,10 +9372,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="60" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F8" s="60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G8" s="60">
         <v>15</v>
@@ -9431,10 +9431,10 @@
         <v>15</v>
       </c>
       <c r="E9" s="61" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F9" s="61" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G9" s="24">
         <v>9</v>
@@ -9578,10 +9578,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="61" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F12" s="61" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G12" s="61">
         <v>16</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="K12" s="61" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L12" s="61">
         <v>14</v>
@@ -9798,10 +9798,10 @@
         <v>7</v>
       </c>
       <c r="E16" s="61" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G16" s="61">
         <v>10</v>
@@ -9851,7 +9851,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="76" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F17" s="67">
         <v>10</v>
@@ -9889,7 +9889,7 @@
       <c r="B18" s="73"/>
       <c r="C18" s="73"/>
       <c r="D18" s="74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E18" s="55">
         <v>268</v>
@@ -9948,7 +9948,7 @@
     </row>
     <row r="21" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G21" s="84" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H21" s="84"/>
       <c r="I21" s="84"/>
